--- a/Packages/cn.etetet.twstilemap/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twstilemap/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -86,37 +86,49 @@
     <t>注释</t>
   </si>
   <si>
-    <t>cn.etetet.twstilemap.LandType</t>
-  </si>
-  <si>
-    <t>Floor</t>
-  </si>
-  <si>
-    <t>地面</t>
-  </si>
-  <si>
-    <t>Build</t>
-  </si>
-  <si>
-    <t>建筑</t>
-  </si>
-  <si>
-    <t>Road</t>
-  </si>
-  <si>
-    <t>道路</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>水</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t>农田</t>
+    <t>cn.etetet.twstilemap.DrawType</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>单个</t>
+  </si>
+  <si>
+    <t>Drag</t>
+  </si>
+  <si>
+    <t>拖拽</t>
+  </si>
+  <si>
+    <t>cn.etetet.twstilemap.TileType</t>
+  </si>
+  <si>
+    <t>Tile</t>
+  </si>
+  <si>
+    <t>地块</t>
+  </si>
+  <si>
+    <t>RuleTile</t>
+  </si>
+  <si>
+    <t>规则地块</t>
+  </si>
+  <si>
+    <t>CustomRuleTile</t>
+  </si>
+  <si>
+    <t>自定义规则地块</t>
+  </si>
+  <si>
+    <t>Sprite</t>
+  </si>
+  <si>
+    <t>精灵</t>
+  </si>
+  <si>
+    <t>代码自动创建tile</t>
   </si>
 </sst>
 </file>
@@ -1079,8 +1091,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
     <col min="2" max="2" width="29.125" customWidth="1"/>
@@ -1208,37 +1220,60 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="8:11">
+    <row r="6" spans="2:11">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="8:11">
+    <row r="7" spans="8:11">
       <c r="H7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="8:11">
       <c r="H8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="8:11">
+      <c r="H9" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twstilemap/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twstilemap/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>cn.etetet.twstilemap.DrawType</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>无</t>
   </si>
   <si>
     <t>Single</t>
@@ -1091,7 +1097,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="7.75" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.75" customWidth="1"/>
@@ -1220,35 +1226,35 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="2:11">
-      <c r="B6" t="s">
+    <row r="6" customFormat="1" spans="8:11">
+      <c r="H6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="b">
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="b">
         <v>0</v>
       </c>
-      <c r="D6" t="b">
+      <c r="D7" t="b">
         <v>1</v>
       </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
       <c r="H7" t="s">
         <v>27</v>
       </c>
       <c r="I7" t="s">
         <v>28</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>
@@ -1273,7 +1279,18 @@
         <v>32</v>
       </c>
       <c r="K9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="8:11">
+      <c r="H10" t="s">
         <v>33</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.twstilemap/Luban/Config/Base/__enums__.xlsx
+++ b/Packages/cn.etetet.twstilemap/Luban/Config/Base/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>拖拽</t>
+  </si>
+  <si>
+    <t>拖拽(当前规则：x，y不能大于1)</t>
   </si>
   <si>
     <t>cn.etetet.twstilemap.TileType</t>
@@ -1234,12 +1237,12 @@
         <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:11">
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
@@ -1248,49 +1251,49 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="8:11">
       <c r="H8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="8:11">
       <c r="H9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="8:11">
       <c r="H10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
